--- a/审查意见_[公开] 集成式备用仪表环境鉴定试验大纲（非电磁类）.xlsx
+++ b/审查意见_[公开] 集成式备用仪表环境鉴定试验大纲（非电磁类）.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>序号</t>
   </si>
@@ -29,82 +29,363 @@
     <t>是否接受</t>
   </si>
   <si>
-    <t>第 1 部分</t>
-  </si>
-  <si>
-    <t>多个表格中序号列留空，应填写序号以增强表格的可读性。
-建议：补充完整表格中的序号列。</t>
-  </si>
-  <si>
-    <t>位置：表 14-1、表 15-1、表 16-1、表 17-1、表 18-1、表 19-1、表 20-1、表 21-1、表 22-1、表 23-1
-规则：表格信息完整性
-严重程度：高</t>
+    <t>温度变化试验</t>
+  </si>
+  <si>
+    <t>受试设备和陪试设备的详细描述引用了其他章节（6.1节、6.4节、6.5节），但未在当前章节给出具体信息。
+建议：补充6.1节、6.4节、6.5节的具体内容，明确受试设备和陪试设备的详细信息。</t>
+  </si>
+  <si>
+    <t>位置：受试/陪试设备部分
+规则：G-1-test_unit
+严重程度：中</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>表 16-1 中部分列未填写具体内容，表 16-2 和表 16-3 中缺少序号列。
-建议：补充完整表格中的信息和序号。</t>
-  </si>
-  <si>
-    <t>位置：表 16-1、表 16-2、表 16-3
-规则：表格信息完整性
-严重程度：高</t>
-  </si>
-  <si>
-    <t>表格中存在列名重复，如“标准振动曲线频率拐点（B3曲线）B3=1.55Grms”和“强化振动曲线频率拐点（B4曲线）：B4=2.20Grms”列名与上一行重复。
-建议：修正列名，避免重复。</t>
-  </si>
-  <si>
-    <t>位置：表 17-1、表 17-2
-规则：表格信息准确性
-严重程度：高</t>
-  </si>
-  <si>
-    <t>文档中提到多个图示，但实际并无图示内容，导致无法直观了解试验布置和连接方式。
-建议：补充相应的图示内容。</t>
-  </si>
-  <si>
-    <t>位置：图 14-1、图 14-2、图 15-1、图 15-2、图 16-1、图 16-2、图 17-1、图 17-2、图 17-3、图 18-1、图 18-2、图 18-3、图 19-1、图 19-2、图 20-1、图 20-2、图 21-1、图 22-1、图 22-2、图 23-1、图 23-2
-规则：图文一致性
-严重程度：中</t>
-  </si>
-  <si>
-    <t>部分表格中加速度传感器和数字式振动控制器的校验方式未给出。
-建议：补充加速度传感器和数字式振动控制器的校验方式。</t>
-  </si>
-  <si>
-    <t>位置：表 17-3、表 18-1、表 19-2、表 20-3、表 21-3、表 22-2、表 23-2
-规则：表格信息完整性
-严重程度：中</t>
-  </si>
-  <si>
-    <t>防水部分中提到的图 18-1、图 18-2 和图 18-3 未在文档中给出。
-建议：补充防水部分缺失的图示。</t>
-  </si>
-  <si>
-    <t>位置：防水部分
-规则：图文一致性
+    <t>表14-2中部分设备的技术要求/精度栏位为空，缺少具体参数。
+建议：补充表14-2中设备的技术要求/精度信息，确保设备参数完整。</t>
+  </si>
+  <si>
+    <t>位置：试验设备、测试设备及要求部分
+规则：G-10-Test equipment and certificates
+严重程度：中</t>
+  </si>
+  <si>
+    <t>图14-3未在文档中提供，缺少温度变化试验控制曲线图。
+建议：补充图14-3：温度变化试验控制曲线图，确保试验程序的完整性。</t>
+  </si>
+  <si>
+    <t>位置：试验程序部分
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>引用了12.2章节的表12-2和QPAT检查要求，但未在当前章节给出具体内容。
+建议：补充12.2章节的表12-2和QPAT检查要求的具体内容，明确试验判据。</t>
+  </si>
+  <si>
+    <t>位置：试验判据部分
+规则：G-15-Test_conditions
+严重程度：中</t>
+  </si>
+  <si>
+    <t>湿热</t>
+  </si>
+  <si>
+    <t>表格中“高温高湿”阶段的“周期数”和“试验允差”列未填写，缺少必要的试验信息。
+建议：补充“高温高湿”阶段的周期数和试验允差信息。</t>
+  </si>
+  <si>
+    <t>位置：表 15-1：湿热试验条件
+规则：G-1-test_unit
+严重程度：中</t>
+  </si>
+  <si>
+    <t>表格中序号列缺失，影响表格的规范性和可读性。
+建议：补充表格中的序号列。</t>
+  </si>
+  <si>
+    <t>位置：表 15-2：设备信息表
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>“湿热试验控制曲线设定应如图 15-3所示”一句中，图15-3未在文档中提供，缺少必要的图形支持。
+建议：提供图15-3的具体内容或说明。</t>
+  </si>
+  <si>
+    <t>位置：试验程序部分
+规则：G-16-pic_sheet
 严重程度：低</t>
   </si>
   <si>
-    <t>流体敏感性部分中提到的图 19-1 和图 19-2 未在文档中给出。
-建议：补充流体敏感性部分缺失的图示。</t>
-  </si>
-  <si>
-    <t>位置：流体敏感性部分
-规则：图文一致性
+    <t>“受试设备：E/ISI-2集成式备用仪表，详细构型见6.1节受试设备构型状态；陪试设备：详见6.5节”中的引用章节未在文档中提供，缺少必要的文档支持。
+建议：提供6.1节和6.5节的具体内容或说明。</t>
+  </si>
+  <si>
+    <t>位置：受试/陪试设备部分
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>“在附录A中记录试验设备相关信息及试验开始和结束时间等内容”中的附录A未在文档中提供，缺少必要的文档支持。
+建议：提供附录A的具体内容或说明。</t>
+  </si>
+  <si>
+    <t>工作冲击和坠撞安全</t>
+  </si>
+  <si>
+    <t>部分表格内容缺失，如表 16-1 中 +Y/－Y 和 +Z/－Z 方向的冲击次数未给出，表 16-2 中同样方向的冲击次数也未给出。
+建议：补充完整表 16-1 和表 16-2 中缺失的冲击次数信息。</t>
+  </si>
+  <si>
+    <t>位置：表 16-1、表 16-2
+规则：G-2-Project_omissions
+严重程度：中</t>
+  </si>
+  <si>
+    <t>引用的图表未在文档中提供，无法验证图表内容的准确性和完整性。
+建议：提供缺失的图表内容，确保图表与文档描述一致。</t>
+  </si>
+  <si>
+    <t>位置：图 16-1、图 16-2、图 16-3、图 16-4、图 16-5、图 16-6
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>表 16-4 中序号列未填写具体序号，影响表格的规范性和可读性。
+建议：补充表 16-4 中的序号列，按照实际顺序填写序号。</t>
+  </si>
+  <si>
+    <t>位置：表 16-4
+规则：G-11-auxiliary_facilities
 严重程度：低</t>
   </si>
   <si>
-    <t>霉菌部分中提到的图 20-1 和图 20-2 未在文档中给出。
-建议：补充霉菌部分缺失的图示。</t>
-  </si>
-  <si>
-    <t>位置：霉菌部分
-规则：图文一致性
+    <t>试验程序中多次提到“按照12.2章节表12-2要求进行QPAT检查”，但文档中未提供12.2章节的具体内容，无法验证QPAT检查的完整性和准确性。
+建议：提供12.2章节的具体内容，或在文档中直接描述QPAT检查的详细要求。</t>
+  </si>
+  <si>
+    <t>位置：试验程序部分
+规则：G-4-Pretest_preparation
+严重程度：中</t>
+  </si>
+  <si>
+    <t>振动</t>
+  </si>
+  <si>
+    <t>缺少传感器安装位置的描述
+建议：补充传感器安装位置的具体描述</t>
+  </si>
+  <si>
+    <t>位置：试验布置和连接
+规则：G-4-Pretest_preparation
+严重程度：中</t>
+  </si>
+  <si>
+    <t>图17-5缺失传感器安装位置的描述
+建议：提供图17-5的补充说明或更新图表以包含传感器安装位置</t>
+  </si>
+  <si>
+    <t>位置：图 17-5：振动试验布置图（缺少传感器安装位置）
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>部分设备序号缺失
+建议：补全设备序号以保持信息的完整性和条理性</t>
+  </si>
+  <si>
+    <t>位置：表 17-3：设备信息表
+规则：G-11-auxiliary_facilities
 严重程度：低</t>
+  </si>
+  <si>
+    <t>陪试设备的具体信息未给出，仅提到详见6.5节，但该章节内容未提供
+建议：提供陪试设备的具体信息或确保6.5节内容的完整性</t>
+  </si>
+  <si>
+    <t>位置：受试/陪试设备
+规则：G-11-auxiliary_facilities
+严重程度：中</t>
+  </si>
+  <si>
+    <t>未明确提及试验前功能性能检查的具体项目和标准
+建议：明确列出试验前功能性能检查的具体项目和标准</t>
+  </si>
+  <si>
+    <t>位置：试验程序
+规则：G-3-functional_check
+严重程度：中</t>
+  </si>
+  <si>
+    <t>防水</t>
+  </si>
+  <si>
+    <t>陪试设备和工作状态的具体内容引用了其他章节，但未在本章节给出具体信息。
+建议：建议在本章节补充陪试设备和工作状态的具体内容，或在引用的章节中明确指出相关信息。</t>
+  </si>
+  <si>
+    <t>表格中部分设备序号缺失，且高低温湿热试验箱的校验方式未给出。
+建议：建议补全表格中的序号，并给出高低温湿热试验箱的校验方式。</t>
+  </si>
+  <si>
+    <t>位置：试验设备、测试设备及要求部分
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>试验程序中多次提到'工作状态1'，但未在本章节或引用章节中明确'工作状态1'的具体含义。
+建议：建议明确'工作状态1'的具体含义，或在相关章节中给出详细描述。</t>
+  </si>
+  <si>
+    <t>位置：试验程序部分
+规则：G-3-functional_check
+严重程度：低</t>
+  </si>
+  <si>
+    <t>试验判据中提到'满足以上要求，则判定结论为Pass，否则为Fail'，但未给出具体的判定标准和要求。
+建议：建议在本章节或引用章节中明确试验判据的具体要求和标准。</t>
+  </si>
+  <si>
+    <t>流体敏感性</t>
+  </si>
+  <si>
+    <t>陪试设备具体信息未给出，仅提到详见6.5节，但文档中未包含6.5节内容。
+建议：补充陪试设备的具体信息或提供6.5节的详细内容。</t>
+  </si>
+  <si>
+    <t>表19-2中部分设备的技术要求/精度列留空，缺少具体参数。
+建议：补充完整表19-2中所有设备的技术要求/精度信息。</t>
+  </si>
+  <si>
+    <t>步骤a)中提到的QPAT1-1、QPAT2、QPAT3和QPAT4检查的具体内容未在文档中给出。
+建议：提供QPAT1-1、QPAT2、QPAT3和QPAT4检查的具体要求和步骤。</t>
+  </si>
+  <si>
+    <t>试验判据中提到的检测记录表见附录A，但文档中未包含附录A的内容。
+建议：补充附录A的内容，明确QPAT1-1、QPAT2、QPAT3和QPAT4检查的检测记录表格式和要求。</t>
+  </si>
+  <si>
+    <t>位置：试验判据部分
+规则：G-4-Pretest_preparation
+严重程度：低</t>
+  </si>
+  <si>
+    <t>霉菌</t>
+  </si>
+  <si>
+    <t>未明确提及试验单位和试验场所
+建议：补充具体的试验单位和试验场所信息</t>
+  </si>
+  <si>
+    <t>位置：试验要求
+规则：G-1-test_unit
+严重程度：中</t>
+  </si>
+  <si>
+    <t>陪试设备信息未提供，仅提到详见6.5节，但该节内容未给出
+建议：补充陪试设备的详细信息</t>
+  </si>
+  <si>
+    <t>位置：受试/陪试设备
+规则：G-1-test_unit
+严重程度：中</t>
+  </si>
+  <si>
+    <t>部分设备的技术要求/精度未给出，如专用测试设备
+建议：补充完整所有设备的详细技术要求和精度信息</t>
+  </si>
+  <si>
+    <t>位置：试验设备、测试设备及要求
+规则：G-10-Test equipment and certificates
+严重程度：中</t>
+  </si>
+  <si>
+    <t>未提及试验前准备检查的具体内容
+建议：补充试验前准备检查的详细步骤和要求</t>
+  </si>
+  <si>
+    <t>位置：试验程序
+规则：G-4-Pretest_preparation
+严重程度：中</t>
+  </si>
+  <si>
+    <t>未提及试验前后功能性能检查的具体内容
+建议：补充试验前后功能性能检查的详细步骤和标准</t>
+  </si>
+  <si>
+    <t>防火，可燃性</t>
+  </si>
+  <si>
+    <t>表格中部分样件名称、图号/型号、材料、尺寸等信息未填写
+建议：补充完整样件名称、图号/型号、材料、尺寸等信息</t>
+  </si>
+  <si>
+    <t>位置：表 21-2：可燃性试验受试样件清单
+规则：G-11-auxiliary_facilities
+严重程度：中</t>
+  </si>
+  <si>
+    <t>表格中部分设备名称、用途、设备型号、技术要求/精度等信息未填写
+建议：补充完整设备名称、用途、设备型号、技术要求/精度等信息</t>
+  </si>
+  <si>
+    <t>位置：表 21-3：设备信息表
+规则：G-10-Test equipment and certificates
+严重程度：中</t>
+  </si>
+  <si>
+    <t>部分步骤描述不够具体，如步骤a)中未明确预处理试验箱的具体条件
+建议：补充明确预处理试验箱的具体条件，如温度、湿度等</t>
+  </si>
+  <si>
+    <t>位置：试验程序
+规则：G-15-Test_conditions
+严重程度：中</t>
+  </si>
+  <si>
+    <t>判据中提到的平均燃烧时间、滴落物燃烧时间、烧焦长度的具体数值未给出单位
+建议：补充明确平均燃烧时间、滴落物燃烧时间、烧焦长度的具体数值单位</t>
+  </si>
+  <si>
+    <t>位置：试验判据
+规则：G-15-Test_conditions
+严重程度：低</t>
+  </si>
+  <si>
+    <t>加速度</t>
+  </si>
+  <si>
+    <t>表格中“结构试验量值”行的“右(Y)”列数值与前一列重复，应为笔误
+建议：将“3 g”更正为“3.0g”</t>
+  </si>
+  <si>
+    <t>位置：表 22-1：加速度试验条件（核实量值）
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>陪试设备具体信息未给出，仅提到详见6.5节，但该章节内容未在文档中提供
+建议：补充陪试设备的具体信息或提供6.5节的详细内容</t>
+  </si>
+  <si>
+    <t>表格中序号列留空，应填写具体序号以保证表格的完整性和清晰性
+建议：为每个设备填写序号</t>
+  </si>
+  <si>
+    <t>位置：试验设备、测试设备及要求
+规则：G-16-pic_sheet
+严重程度：中</t>
+  </si>
+  <si>
+    <t>步骤c)中提到的“工作状态2”未在文档中定义，表述不明确
+建议：明确“工作状态2”的具体含义或提供相关定义</t>
+  </si>
+  <si>
+    <t>虽然提到了按12.2章节要求进行QPAT检查，但未说明QPAT的具体含义或流程
+建议：提供QPAT的具体定义或流程描述</t>
+  </si>
+  <si>
+    <t>风车</t>
+  </si>
+  <si>
+    <t>陪试设备的具体信息未给出，仅提到详见6.5节，但文档中未包含6.5节内容。
+建议：补充陪试设备的具体信息或提供6.5节的详细内容。</t>
+  </si>
+  <si>
+    <t>设备信息表中部分设备的技术要求/精度列显示为'/'，表示信息缺失。
+建议：补充完整所有设备的技术要求和精度信息。</t>
+  </si>
+  <si>
+    <t>提及的图 23-1和图 23-2未在文档中给出。
+建议：提供图 23-1和图 23-2的具体内容或说明。</t>
+  </si>
+  <si>
+    <t>试验判据中提到的12.2章节表12-2未在文档中给出。
+建议：提供12.2章节表12-2的具体内容或说明。</t>
   </si>
 </sst>
 </file>
@@ -188,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.8125" customWidth="true"/>
@@ -288,13 +569,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="2">
         <v>8</v>
@@ -305,13 +586,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>8</v>
@@ -322,13 +603,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>8</v>
@@ -339,15 +620,627 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n" s="2">
+        <v>33.0</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s" s="2">
+      <c r="E44" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n" s="2">
+        <v>44.0</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>8</v>
       </c>
     </row>
